--- a/data/trans_bre/IP18A01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 10,54</t>
+          <t>-6,44; 10,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 4,85</t>
+          <t>-15,61; 4,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 12,38</t>
+          <t>-4,44; 11,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 0,0</t>
+          <t>-24,68; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-61,61; 507,95</t>
+          <t>-62,73; 385,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-81,96; 75,18</t>
+          <t>-80,95; 69,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-56,77; 724,27</t>
+          <t>-56,03; 563,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 10,76</t>
+          <t>-3,78; 10,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 3,39</t>
+          <t>-8,1; 3,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 6,32</t>
+          <t>-8,8; 4,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 35,86</t>
+          <t>-0,83; 35,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,41; 238,84</t>
+          <t>-35,13; 187,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,6; 82,4</t>
+          <t>-74,68; 96,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,97; 122,74</t>
+          <t>-72,1; 89,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 6,9</t>
+          <t>-4,55; 6,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 1,52</t>
+          <t>-16,69; 1,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 12,07</t>
+          <t>-6,09; 11,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 0,0</t>
+          <t>-21,35; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-85,68; 693,03</t>
+          <t>-81,46; 508,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,42; 29,48</t>
+          <t>-83,97; 27,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-50,26; 263,18</t>
+          <t>-50,74; 226,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 4,86</t>
+          <t>-7,85; 4,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 7,94</t>
+          <t>-7,08; 8,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 8,27</t>
+          <t>-3,01; 9,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 23,72</t>
+          <t>-13,66; 23,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,19; 190,91</t>
+          <t>-82,02; 167,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,74; 217,7</t>
+          <t>-64,91; 234,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 14,35</t>
+          <t>-6,25; 13,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 9,52</t>
+          <t>-8,87; 9,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 6,03</t>
+          <t>-11,91; 4,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-84,5; 198,68</t>
+          <t>-86,39; 185,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 7,19</t>
+          <t>-7,06; 8,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 10,15</t>
+          <t>-9,83; 10,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 13,39</t>
+          <t>-11,03; 11,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 33,28</t>
+          <t>-0,51; 40,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,85; 520,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,43; 165,29</t>
+          <t>-66,04; 203,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-54,02; 133,55</t>
+          <t>-52,42; 134,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,37 +1260,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 2,37</t>
+          <t>-7,76; 2,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 6,62</t>
+          <t>-6,47; 7,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 8,39</t>
+          <t>-8,2; 7,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 22,75</t>
+          <t>1,8; 23,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-72,34; 45,61</t>
+          <t>-68,64; 51,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-43,39; 71,16</t>
+          <t>-41,42; 77,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-42,65; 73,82</t>
+          <t>-42,27; 62,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 7,25</t>
+          <t>-6,44; 7,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 11,05</t>
+          <t>-0,39; 10,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 5,03</t>
+          <t>-3,4; 5,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 10,87</t>
+          <t>-17,0; 10,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,38; 66,62</t>
+          <t>-36,98; 69,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,48; 218,2</t>
+          <t>-4,97; 217,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-46,69; 148,35</t>
+          <t>-47,74; 157,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,63</t>
+          <t>-2,49; 2,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 2,54</t>
+          <t>-2,85; 2,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,37</t>
+          <t>-1,94; 3,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 9,46</t>
+          <t>-1,13; 9,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 40,07</t>
+          <t>-25,11; 40,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 28,98</t>
+          <t>-25,08; 30,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 45,02</t>
+          <t>-19,34; 47,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 420,35</t>
+          <t>-28,56; 410,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Provincia-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 10,21</t>
+          <t>-6,38; 9,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 4,88</t>
+          <t>-16,95; 5,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 11,38</t>
+          <t>-4,41; 11,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,68; 0,0</t>
+          <t>-23,23; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-62,73; 385,85</t>
+          <t>-66,37; 357,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,95; 69,76</t>
+          <t>-82,08; 78,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-56,03; 563,38</t>
+          <t>-58,48; 646,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 10,01</t>
+          <t>-3,46; 9,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 3,58</t>
+          <t>-8,54; 3,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 4,64</t>
+          <t>-8,13; 6,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 35,42</t>
+          <t>-1,18; 37,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 187,84</t>
+          <t>-32,17; 197,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,68; 96,91</t>
+          <t>-74,21; 89,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,1; 89,14</t>
+          <t>-66,66; 135,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 6,58</t>
+          <t>-4,31; 6,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 1,72</t>
+          <t>-17,39; 1,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 11,64</t>
+          <t>-6,39; 11,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 0,0</t>
+          <t>-17,94; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-81,46; 508,99</t>
+          <t>-83,26; 609,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,97; 27,69</t>
+          <t>-83,08; 23,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-50,74; 226,2</t>
+          <t>-51,56; 235,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 4,8</t>
+          <t>-7,85; 4,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 8,17</t>
+          <t>-6,96; 7,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 9,46</t>
+          <t>-3,01; 8,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 23,81</t>
+          <t>-11,8; 25,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,02; 167,77</t>
+          <t>-82,67; 160,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,91; 234,61</t>
+          <t>-63,97; 177,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 13,9</t>
+          <t>-6,06; 14,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 9,59</t>
+          <t>-8,7; 9,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 4,83</t>
+          <t>-11,9; 4,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 451,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-86,39; 185,69</t>
+          <t>-90,18; 160,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 8,11</t>
+          <t>-5,86; 8,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 10,76</t>
+          <t>-10,05; 9,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 11,86</t>
+          <t>-11,21; 12,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 40,37</t>
+          <t>-2,04; 40,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,85; 520,94</t>
+          <t>-81,31; 618,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,04; 203,64</t>
+          <t>-61,83; 187,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,42; 134,11</t>
+          <t>-52,59; 125,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,37 +1260,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 2,46</t>
+          <t>-7,87; 2,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 7,05</t>
+          <t>-6,36; 6,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 7,67</t>
+          <t>-8,07; 7,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 23,45</t>
+          <t>1,8; 25,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-68,64; 51,26</t>
+          <t>-71,14; 60,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-41,42; 77,4</t>
+          <t>-42,87; 73,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-42,27; 62,71</t>
+          <t>-42,38; 70,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 7,98</t>
+          <t>-7,26; 7,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 10,75</t>
+          <t>-0,03; 10,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 5,08</t>
+          <t>-2,92; 5,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 10,31</t>
+          <t>-15,41; 10,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 69,15</t>
+          <t>-40,35; 62,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 217,98</t>
+          <t>-1,01; 224,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,74; 157,55</t>
+          <t>-40,79; 175,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,84</t>
+          <t>-2,42; 2,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 2,66</t>
+          <t>-2,63; 2,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,47</t>
+          <t>-1,99; 3,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 9,21</t>
+          <t>-1,09; 8,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 40,48</t>
+          <t>-24,33; 37,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 30,85</t>
+          <t>-22,89; 29,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 47,03</t>
+          <t>-19,62; 42,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-28,56; 410,84</t>
+          <t>-31,08; 390,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores cuya última consulta médica fue por vacunación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-7,47</t>
+          <t>-7,61</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 9,6</t>
+          <t>-5,22; 10,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 5,21</t>
+          <t>-17,01; 4,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 11,9</t>
+          <t>-3,79; 12,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,23; 0,0</t>
+          <t>-25,78; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,37; 357,48</t>
+          <t>-61,61; 507,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-82,08; 78,75</t>
+          <t>-81,96; 75,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-58,48; 646,4</t>
+          <t>-56,77; 724,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,92</t>
+          <t>12,73</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>271,37%</t>
+          <t>313,19%</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 9,63</t>
+          <t>-3,53; 10,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 3,37</t>
+          <t>-8,67; 3,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 6,66</t>
+          <t>-8,41; 6,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 37,25</t>
+          <t>-0,06; 35,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 197,18</t>
+          <t>-32,41; 238,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,21; 89,96</t>
+          <t>-79,6; 82,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,66; 135,77</t>
+          <t>-66,97; 122,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,0</t>
+          <t>-3,73</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 6,76</t>
+          <t>-4,57; 6,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 1,33</t>
+          <t>-16,21; 1,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 11,42</t>
+          <t>-6,0; 12,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 0,0</t>
+          <t>-17,28; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-83,26; 609,65</t>
+          <t>-85,68; 693,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,08; 23,35</t>
+          <t>-83,42; 29,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-51,56; 235,09</t>
+          <t>-50,26; 263,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>1,61</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 4,51</t>
+          <t>-7,69; 4,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 7,32</t>
+          <t>-6,48; 7,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 8,65</t>
+          <t>-3,05; 8,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 25,27</t>
+          <t>-10,71; 25,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,67; 160,89</t>
+          <t>-80,19; 190,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,97; 177,49</t>
+          <t>-63,74; 217,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 14,11</t>
+          <t>-4,38; 14,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 9,06</t>
+          <t>-8,76; 9,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 4,91</t>
+          <t>-11,44; 6,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 451,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-90,18; 160,53</t>
+          <t>-84,5; 198,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,09</t>
+          <t>9,28</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>480,85%</t>
+          <t>541,42%</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 8,12</t>
+          <t>-5,68; 7,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 9,97</t>
+          <t>-10,12; 10,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 12,48</t>
+          <t>-11,55; 13,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 40,94</t>
+          <t>-1,71; 33,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-81,31; 618,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,83; 187,92</t>
+          <t>-64,43; 165,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-52,59; 125,82</t>
+          <t>-54,02; 133,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,67</t>
+          <t>9,74</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1260,37 +1260,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 2,93</t>
+          <t>-7,92; 2,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 6,55</t>
+          <t>-6,56; 6,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 7,47</t>
+          <t>-8,46; 8,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 25,87</t>
+          <t>1,77; 26,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-71,14; 60,49</t>
+          <t>-72,34; 45,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-42,87; 73,04</t>
+          <t>-43,39; 71,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 70,54</t>
+          <t>-42,65; 73,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1,04</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-13,92%</t>
+          <t>-16,66%</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 7,14</t>
+          <t>-6,1; 7,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 10,72</t>
+          <t>0,36; 11,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 5,32</t>
+          <t>-3,02; 5,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 10,65</t>
+          <t>-16,75; 10,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,35; 62,23</t>
+          <t>-36,38; 66,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 224,24</t>
+          <t>0,48; 218,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 175,27</t>
+          <t>-46,69; 148,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>3,42</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,8</t>
+          <t>-2,41; 2,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,58</t>
+          <t>-2,91; 2,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,19</t>
+          <t>-1,71; 3,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 8,81</t>
+          <t>-1,1; 9,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 37,78</t>
+          <t>-26,3; 40,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 29,32</t>
+          <t>-25,77; 28,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 42,47</t>
+          <t>-17,06; 45,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 390,59</t>
+          <t>-29,5; 457,09</t>
         </is>
       </c>
     </row>
